--- a/data/Terre di Pedemonte/investment_decision/Verscio_SFH_until_2004_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_SFH_until_2004_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>483.8811514734164</v>
+        <v>156.5883974382549</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>146556.9874845998</v>
       </c>
       <c r="F2" t="n">
-        <v>483.8811514734164</v>
+        <v>156.5883974382549</v>
       </c>
       <c r="G2" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="H2" t="n">
-        <v>483.8811514734164</v>
+        <v>156.5883974382549</v>
       </c>
       <c r="I2" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="J2" t="n">
-        <v>483.8811514734164</v>
+        <v>156.5883974382549</v>
       </c>
       <c r="K2" t="n">
         <v>146556.9874845998</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>866.7394469462563</v>
+        <v>446.5041415811929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>146556.9874845998</v>
       </c>
       <c r="F3" t="n">
-        <v>811.9882512467755</v>
+        <v>455.0603514601138</v>
       </c>
       <c r="G3" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="H3" t="n">
-        <v>925.2857876066985</v>
+        <v>441.8417402435486</v>
       </c>
       <c r="I3" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="J3" t="n">
-        <v>844.7405344063903</v>
+        <v>446.2856275744239</v>
       </c>
       <c r="K3" t="n">
         <v>146556.9874845998</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>866.7394469462563</v>
+        <v>656.963001107135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>146556.9874845998</v>
       </c>
       <c r="F4" t="n">
-        <v>811.9882512467755</v>
+        <v>656.9630011071361</v>
       </c>
       <c r="G4" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="H4" t="n">
-        <v>925.2857876066985</v>
+        <v>656.9630011071354</v>
       </c>
       <c r="I4" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="J4" t="n">
-        <v>844.7405344063903</v>
+        <v>656.57257770286</v>
       </c>
       <c r="K4" t="n">
         <v>146556.9874845998</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>1043.673485411685</v>
+        <v>678.7857376397029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>146556.9874845998</v>
       </c>
       <c r="F5" t="n">
-        <v>832.0263704536665</v>
+        <v>678.7857376397022</v>
       </c>
       <c r="G5" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="H5" t="n">
-        <v>1019.430499499787</v>
+        <v>680.4038187280537</v>
       </c>
       <c r="I5" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="J5" t="n">
-        <v>844.7405344063903</v>
+        <v>680.0360441595767</v>
       </c>
       <c r="K5" t="n">
         <v>146556.9874845998</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>1043.673485411685</v>
+        <v>678.7857376397029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>146556.9874845998</v>
       </c>
       <c r="F6" t="n">
-        <v>832.0263704536663</v>
+        <v>678.7857376397023</v>
       </c>
       <c r="G6" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="H6" t="n">
-        <v>1019.430499499787</v>
+        <v>680.4038187280537</v>
       </c>
       <c r="I6" t="n">
         <v>146556.9874845998</v>
       </c>
       <c r="J6" t="n">
-        <v>844.7405344063903</v>
+        <v>680.0360441595767</v>
       </c>
       <c r="K6" t="n">
         <v>146556.9874845998</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>219.8354812268997</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>125.1874008154477</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>219.8354812268997</v>
+        <v>134.8755263617805</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>125.1874008154477</v>
+        <v>134.8755263617805</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>219.8354812268997</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>152.3886389595805</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>219.8354812268997</v>
+        <v>164.181840643284</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>152.3886389595805</v>
+        <v>164.181840643284</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>219.8354812268997</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>163.5310864217708</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>219.8354812268997</v>
+        <v>176.1865907749438</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>163.5310864217708</v>
+        <v>176.1865907749438</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>219.8354812268997</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>169.4872345026348</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>219.8354812268997</v>
+        <v>182.6036790942352</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>169.4872345026348</v>
+        <v>182.6036790942352</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>219.8354812268997</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>173.2090590380118</v>
+        <v>236.8483253932584</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>219.8354812268997</v>
+        <v>186.6135318427172</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>173.2090590380118</v>
+        <v>186.6135318427172</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03331150030706705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03666770335058824</v>
+        <v>0.03276262049309482</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03666770335058824</v>
+        <v>0.0333096797278729</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03276262049309484</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03666770335058824</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03374684656982638</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03666770335058824</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03666770335058823</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03666770335058837</v>
+        <v>0.03347920740705883</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03666770335058824</v>
+        <v>0.03374684656982638</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03666770335058823</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03666770335058823</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03567557265436509</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03590107460312556</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03666770335058824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03985619929411766</v>
+        <v>0.03666770335058824</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03985619929411765</v>
+        <v>0.03567557265436509</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03985619929411766</v>
+        <v>0.03590107460312564</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>1.693888469999998</v>
+        <v>5.039845558061414</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>28.457326296</v>
       </c>
       <c r="F19" t="n">
-        <v>1.693888469999998</v>
+        <v>5.039845558061412</v>
       </c>
       <c r="G19" t="n">
         <v>28.457326296</v>
       </c>
       <c r="H19" t="n">
-        <v>1.693888469999998</v>
+        <v>4.530374356966456</v>
       </c>
       <c r="I19" t="n">
         <v>28.457326296</v>
       </c>
       <c r="J19" t="n">
-        <v>1.693888469999998</v>
+        <v>4.689531647373633</v>
       </c>
       <c r="K19" t="n">
         <v>28.457326296</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>1.693888469999998</v>
+        <v>7.622498115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>28.457326296</v>
       </c>
       <c r="F20" t="n">
-        <v>1.693888469999998</v>
+        <v>7.622498115</v>
       </c>
       <c r="G20" t="n">
         <v>28.457326296</v>
       </c>
       <c r="H20" t="n">
-        <v>1.693888469999998</v>
+        <v>4.530374356966456</v>
       </c>
       <c r="I20" t="n">
         <v>28.457326296</v>
       </c>
       <c r="J20" t="n">
-        <v>1.693888469999998</v>
+        <v>4.689531647373633</v>
       </c>
       <c r="K20" t="n">
         <v>28.457326296</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>1.693888469999998</v>
+        <v>7.622498115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>28.457326296</v>
       </c>
       <c r="F21" t="n">
-        <v>1.693888469999998</v>
+        <v>7.622498115</v>
       </c>
       <c r="G21" t="n">
         <v>28.457326296</v>
       </c>
       <c r="H21" t="n">
-        <v>1.693888469999998</v>
+        <v>4.530374356966456</v>
       </c>
       <c r="I21" t="n">
         <v>28.457326296</v>
       </c>
       <c r="J21" t="n">
-        <v>1.693888469999998</v>
+        <v>4.689531647373633</v>
       </c>
       <c r="K21" t="n">
         <v>28.457326296</v>
@@ -1551,13 +1551,13 @@
         <v>28.457326296</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.5270694323685459</v>
       </c>
       <c r="I30" t="n">
         <v>28.457326296</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.4072715220894794</v>
       </c>
       <c r="K30" t="n">
         <v>28.457326296</v>
@@ -1588,13 +1588,13 @@
         <v>28.457326296</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.5270694323685459</v>
       </c>
       <c r="I31" t="n">
         <v>28.457326296</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.4072715220894794</v>
       </c>
       <c r="K31" t="n">
         <v>28.457326296</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>299.2458573015285</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>173.5102195686378</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>299.2458573015285</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>299.2458573015285</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>210.9603411321029</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>299.2458573015285</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>299.2458573015285</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>226.3833495631317</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>299.2458573015285</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>299.2458573015285</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>234.7438790604208</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>299.2458573015285</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>299.2458573015285</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>240.0570163378557</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>299.2458573015285</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>64.17250309171068</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>25.23892510145064</v>
+        <v>12.94037927897386</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F53" t="n">
-        <v>25.14550047641979</v>
+        <v>12.22597017919177</v>
       </c>
       <c r="G53" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H53" t="n">
+        <v>13.09816690395933</v>
+      </c>
+      <c r="I53" t="n">
         <v>84.41784627191794</v>
       </c>
-      <c r="H53" t="n">
-        <v>20.81790841598772</v>
-      </c>
-      <c r="I53" t="n">
-        <v>204.5306553291199</v>
-      </c>
       <c r="J53" t="n">
-        <v>19.72858153354561</v>
+        <v>11.29014900544175</v>
       </c>
       <c r="K53" t="n">
         <v>84.41784627191794</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>63.81462807757338</v>
+        <v>63.37655091699955</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F54" t="n">
-        <v>63.3171187768684</v>
+        <v>57.86903548443292</v>
       </c>
       <c r="G54" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H54" t="n">
+        <v>62.8019387802752</v>
+      </c>
+      <c r="I54" t="n">
         <v>93.44016756124408</v>
       </c>
-      <c r="H54" t="n">
-        <v>60.75949990568621</v>
-      </c>
-      <c r="I54" t="n">
-        <v>204.5306553291199</v>
-      </c>
       <c r="J54" t="n">
-        <v>59.21635562710804</v>
+        <v>56.62788607310658</v>
       </c>
       <c r="K54" t="n">
         <v>93.44016756124408</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>66.46795929914437</v>
+        <v>64.92685349951297</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F55" t="n">
-        <v>66.65273596307507</v>
+        <v>61.33327238995464</v>
       </c>
       <c r="G55" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H55" t="n">
+        <v>64.96227696269737</v>
+      </c>
+      <c r="I55" t="n">
         <v>98.30931844566148</v>
       </c>
-      <c r="H55" t="n">
-        <v>63.78153870502621</v>
-      </c>
-      <c r="I55" t="n">
-        <v>204.5306553291199</v>
-      </c>
       <c r="J55" t="n">
-        <v>62.06594954494776</v>
+        <v>61.07682156907948</v>
       </c>
       <c r="K55" t="n">
         <v>98.30931844566148</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>64.80785308911301</v>
+        <v>64.76136276756841</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F56" t="n">
-        <v>63.66701859689988</v>
+        <v>60.4487888425611</v>
       </c>
       <c r="G56" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H56" t="n">
+        <v>64.36461786352497</v>
+      </c>
+      <c r="I56" t="n">
         <v>101.3150764662294</v>
       </c>
-      <c r="H56" t="n">
-        <v>61.44048839733473</v>
-      </c>
-      <c r="I56" t="n">
-        <v>204.5306553291199</v>
-      </c>
       <c r="J56" t="n">
-        <v>60.42343681887751</v>
+        <v>60.48151536315076</v>
       </c>
       <c r="K56" t="n">
         <v>101.3150764662294</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>64.17250309171068</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>84.41784627191794</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>93.44016756124408</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>98.30931844566148</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>204.5306553291199</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>101.3150764662294</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>204.5306553291199</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2766,19 +2766,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F63" t="n">
-        <v>1.301171588989994</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="H63" t="n">
-        <v>3.129553288541387</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="J63" t="n">
-        <v>4.906286815018783</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>204.5306553291199</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>31.42429702387724</v>
+        <v>8.85527170464789</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F64" t="n">
-        <v>33.12955328854135</v>
+        <v>13.9379421349655</v>
       </c>
       <c r="G64" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="H64" t="n">
-        <v>33.18796179884291</v>
+        <v>9.429883841372224</v>
       </c>
       <c r="I64" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="J64" t="n">
-        <v>35.41851272145634</v>
+        <v>13.94734572232565</v>
       </c>
       <c r="K64" t="n">
         <v>204.5306553291199</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>36.86800907145123</v>
+        <v>18.41917853011346</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F65" t="n">
-        <v>41.35191876688857</v>
+        <v>21.58791463742282</v>
       </c>
       <c r="G65" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="H65" t="n">
-        <v>40.08920141362594</v>
+        <v>18.42473925498947</v>
       </c>
       <c r="I65" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="J65" t="n">
-        <v>44.56891880361662</v>
+        <v>20.65663016109837</v>
       </c>
       <c r="K65" t="n">
         <v>204.5306553291199</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>49.09633707130305</v>
+        <v>18.58466926205803</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F66" t="n">
-        <v>54.90585792288424</v>
+        <v>22.89724318706534</v>
       </c>
       <c r="G66" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="H66" t="n">
-        <v>52.9984735111379</v>
+        <v>19.02239835416188</v>
       </c>
       <c r="I66" t="n">
         <v>204.5306553291199</v>
       </c>
       <c r="J66" t="n">
-        <v>57.86898020194946</v>
+        <v>22.8961855351823</v>
       </c>
       <c r="K66" t="n">
         <v>204.5306553291199</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>6.330025748399891</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>6.330025748399891</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>9.803641157239637</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>9.803641157239637</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>12.09367765540846</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>12.09367765540846</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>13.76123732645462</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>13.76123732645462</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>15.05205746863052</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>15.05205746863052</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="77">
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>6.330025748399891</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>6.330025748399891</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="78">
@@ -3321,10 +3321,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>0.4248450022489982</v>
       </c>
       <c r="G78" t="n">
-        <v>9.803641157239637</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="J78" t="n">
-        <v>1.089326882442119</v>
+        <v>1.644249168155245</v>
       </c>
       <c r="K78" t="n">
-        <v>9.803641157239637</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="79">
@@ -3358,10 +3358,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>0.4248450022489982</v>
       </c>
       <c r="G79" t="n">
-        <v>12.09367765540846</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3370,10 +3370,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="J79" t="n">
-        <v>1.089326882442119</v>
+        <v>1.644249168155245</v>
       </c>
       <c r="K79" t="n">
-        <v>12.09367765540846</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="80">
@@ -3395,10 +3395,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.4248450022489982</v>
       </c>
       <c r="G80" t="n">
-        <v>13.76123732645462</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>204.5306553291199</v>
       </c>
       <c r="J80" t="n">
-        <v>1.089326882442119</v>
+        <v>1.644249168155245</v>
       </c>
       <c r="K80" t="n">
-        <v>13.76123732645462</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>15.05205746863052</v>
+        <v>204.5306553291199</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>15.05205746863052</v>
+        <v>204.5306553291199</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
